--- a/_Drive/Publicacoes/durval.xlsx
+++ b/_Drive/Publicacoes/durval.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" windowWidth="14400" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="durval.doi" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,35 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3" count="3">
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>10.1088/1742-6596/167/1/012012</t>
+  </si>
+  <si>
+    <t>10.1088/0953-2048/23/11/115012</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <vertAlign val="baseline"/>
+      <sz val="10"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <u val="none"/>
       <color rgb="FF000000"/>
@@ -62,8 +86,12 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -76,490 +104,492 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" style="0" width="9.142307692307693"/>
+    <col min="1" max="1" style="0" width="39.28335336538462" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" style="0" width="9.142307692307693"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>10.1016/j.msea.2005.08.218</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2014.2364779</t>
+          <t>10.1016/j.msea.2005.08.218</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.1088/1742-6596/167/1/012012</t>
+          <t>10.1109/tasc.2014.2364779</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10.1109/tasc.2003.812798</t>
-        </is>
+      <c r="A4" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1016/j.jmatprotec.2006.11.012</t>
+          <t>10.1109/tasc.2003.812798</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1016/j.matlet.2012.09.100</t>
+          <t>10.1016/j.jmatprotec.2006.11.012</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1088/1742-6596/97/1/012127</t>
+          <t>10.1016/j.matlet.2012.09.100</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/DDF.312-315.1228</t>
+          <t>10.1088/1742-6596/97/1/012127</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2006.10.083</t>
+          <t>10.4028/www.scientific.net/DDF.312-315.1228</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1088/1742-6596/43/1/017</t>
+          <t>10.1016/j.msea.2006.10.083</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/28/2/025008</t>
+          <t>10.1088/1742-6596/43/1/017</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1088/1361-6668/ab7471</t>
+          <t>10.1088/0953-2048/28/2/025008</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1109/77.402881</t>
+          <t>10.1088/1361-6668/ab7471</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2010.2093104</t>
+          <t>10.1109/77.402881</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.17563/rbav.v31i1-2.935</t>
+          <t>10.1109/TASC.2010.2093104</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.02.083</t>
+          <t>10.17563/rbav.v31i1-2.935</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1063/1.112146</t>
+          <t>10.1016/j.physc.2004.02.083</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2009.2018471</t>
+          <t>10.1063/1.112146</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2009.2018117</t>
+          <t>10.1109/TASC.2009.2018471</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.03.172</t>
+          <t>10.1109/TASC.2009.2018117</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1590/S0370-44672008000100004</t>
+          <t>10.1016/j.physc.2004.03.172</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.660-661.82</t>
+          <t>10.1590/S0370-44672008000100004</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/DDF.258-260.146</t>
+          <t>10.4028/www.scientific.net/MSF.660-661.82</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.869.29</t>
+          <t>10.4028/www.scientific.net/DDF.258-260.146</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.1103/physrevb.100.125411</t>
+          <t>10.4028/www.scientific.net/MSF.869.29</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2003.812342</t>
+          <t>10.1103/physrevb.100.125411</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/23/11/115012</t>
+          <t>10.1109/tasc.2003.812342</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>10.1007/bf00728437</t>
-        </is>
+      <c r="A28" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1088/1742-6596/43/1/011</t>
+          <t>10.1007/bf00728437</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2018.2807361</t>
+          <t>10.1088/1742-6596/43/1/011</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.802.51</t>
+          <t>10.1109/tasc.2018.2807361</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.02.038</t>
+          <t>10.4028/www.scientific.net/msf.802.51</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10.1590/1516-731320200026</t>
+          <t>10.1016/j.physc.2004.02.038</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2019.2900352</t>
+          <t>10.1590/1516-731320200026</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10.1088/1742-6596/507/1/012043</t>
+          <t>10.1109/tasc.2019.2900352</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10.1590/0366-69132021673812908</t>
+          <t>10.1088/1742-6596/507/1/012043</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10.1016/j.phpro.2012.06.219</t>
+          <t>10.1590/0366-69132021673812908</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.727-728.1158</t>
+          <t>10.1016/j.phpro.2012.06.219</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2010.2092407</t>
+          <t>10.4028/www.scientific.net/MSF.727-728.1158</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10.1007/BF02562901</t>
+          <t>10.1109/TASC.2010.2092407</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2014.2387698</t>
+          <t>10.1007/BF02562901</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2005.848914</t>
+          <t>10.1109/tasc.2014.2387698</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.802.56</t>
+          <t>10.1109/tasc.2005.848914</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/AST.63.414</t>
+          <t>10.4028/www.scientific.net/msf.802.56</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10.1109/77.784792</t>
+          <t>10.4028/www.scientific.net/AST.63.414</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10.1016/j.ssc.2010.04.036</t>
+          <t>10.1109/77.784792</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10.1016/j.indcrop.2018.07.037</t>
+          <t>10.1016/j.ssc.2010.04.036</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10.1088/2053-1583/abbc5f</t>
+          <t>10.1016/j.indcrop.2018.07.037</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10.1515/amm-2015-0492</t>
+          <t>10.1088/2053-1583/abbc5f</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10.1088/1361-648x/aab722</t>
+          <t>10.1515/amm-2015-0492</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10.1089/104454704773660967</t>
+          <t>10.1088/1361-648x/aab722</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.03.100</t>
+          <t>10.1089/104454704773660967</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/AMR.975.128</t>
+          <t>10.1016/j.physc.2004.03.100</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2016.2542289</t>
+          <t>10.4028/www.scientific.net/AMR.975.128</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10.1590/S1516-14392000000400002</t>
+          <t>10.1109/tasc.2016.2542289</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.498-499.316</t>
+          <t>10.1590/S1516-14392000000400002</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10.1109/77.402922</t>
+          <t>10.4028/www.scientific.net/msf.498-499.316</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10.1016/j.biortech.2009.09.034</t>
+          <t>10.1109/77.402922</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.03.173</t>
+          <t>10.1016/j.biortech.2009.09.034</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2009.11.011</t>
+          <t>10.1016/j.physc.2004.03.173</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.899.400</t>
+          <t>10.1016/j.jallcom.2009.11.011</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2018.2816100</t>
+          <t>10.4028/www.scientific.net/MSF.899.400</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.03.164</t>
+          <t>10.1109/tasc.2018.2816100</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10.17563/rbav.v34i3.1005</t>
+          <t>10.1016/j.physc.2004.03.164</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10.1109/77.402880</t>
+          <t>10.17563/rbav.v34i3.1005</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10.1109/tasc.2007.897988</t>
+          <t>10.1109/77.402880</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10.1016/j.surfcoat.2010.06.067</t>
+          <t>10.1109/tasc.2007.897988</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10.1088/1742-6596/1559/1/012058</t>
+          <t>10.1016/j.surfcoat.2010.06.067</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="inlineStr">
+        <is>
+          <t>10.1088/1742-6596/1559/1/012058</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>10.1109/tasc.2005.847645</t>
         </is>
